--- a/public/exports/29189935.xlsx
+++ b/public/exports/29189935.xlsx
@@ -381,7 +381,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5003564</t>
+          <t xml:space="preserve">338409, 338410, 338411</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -390,7 +390,7 @@
         </is>
       </c>
       <c r="F8">
-        <v>512</v>
+        <v>1180</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5004909</t>
+          <t xml:space="preserve">338462, 338463</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F9">
-        <v>817</v>
+        <v>2225</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5004909</t>
+          <t xml:space="preserve">5006098</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F10">
-        <v>4362</v>
+        <v>2781</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5004909</t>
+          <t xml:space="preserve">5006098</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F11">
-        <v>399</v>
+        <v>782</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -586,11 +586,11 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F12">
-        <v>2781</v>
+        <v>1499</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5006098</t>
+          <t xml:space="preserve">5006203</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F13">
-        <v>782</v>
+        <v>625</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5006098</t>
+          <t xml:space="preserve">5006203</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F14">
-        <v>1499</v>
+        <v>721</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5006203</t>
+          <t xml:space="preserve">5009707</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="F15">
-        <v>625</v>
+        <v>397</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5006203</t>
+          <t xml:space="preserve">5009707</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F16">
-        <v>721</v>
+        <v>598</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5007601</t>
+          <t xml:space="preserve">5009707</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F17">
-        <v>5595</v>
+        <v>850</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5007601</t>
+          <t xml:space="preserve">5015548</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F18">
-        <v>350</v>
+        <v>943</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5009707</t>
+          <t xml:space="preserve">5015548</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F19">
-        <v>397</v>
+        <v>585</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5009707</t>
+          <t xml:space="preserve">5015548</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F20">
-        <v>598</v>
+        <v>1088</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5009707</t>
+          <t xml:space="preserve">5015548</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F21">
-        <v>850</v>
+        <v>1108</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5013631</t>
+          <t xml:space="preserve">5015548</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F22">
-        <v>1154</v>
+        <v>1444</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1136,11 +1136,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F23">
-        <v>943</v>
+        <v>311</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5015548</t>
+          <t xml:space="preserve">5017120</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F24">
-        <v>585</v>
+        <v>1031</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5015548</t>
+          <t xml:space="preserve">5721212</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F25">
-        <v>1088</v>
+        <v>744</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5015548</t>
+          <t xml:space="preserve">5721227</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F26">
-        <v>1108</v>
+        <v>4652</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5015548</t>
+          <t xml:space="preserve">5721713</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F27">
-        <v>1444</v>
+        <v>757</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5015548</t>
+          <t xml:space="preserve">5721809</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F28">
-        <v>311</v>
+        <v>2380</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5017120</t>
+          <t xml:space="preserve">5721924</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="F29">
-        <v>1031</v>
+        <v>348</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721212</t>
+          <t xml:space="preserve">5721924</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F30">
-        <v>744</v>
+        <v>351</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721227</t>
+          <t xml:space="preserve">5722450</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="F31">
-        <v>4652</v>
+        <v>300</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721713</t>
+          <t xml:space="preserve">5722450</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F32">
-        <v>757</v>
+        <v>300</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721809</t>
+          <t xml:space="preserve">5722450</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F33">
-        <v>2380</v>
+        <v>300</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721924</t>
+          <t xml:space="preserve">5724047</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="F34">
-        <v>348</v>
+        <v>820</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721924</t>
+          <t xml:space="preserve">5724388</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="F35">
-        <v>351</v>
+        <v>448</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5722450</t>
+          <t xml:space="preserve">5724388</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F36">
-        <v>300</v>
+        <v>1333</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,16 +1831,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5722450</t>
+          <t xml:space="preserve">7162298</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F37">
-        <v>300</v>
+        <v>381</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,16 +1881,16 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5722450</t>
+          <t xml:space="preserve">7162392</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F38">
-        <v>300</v>
+        <v>1657</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1931,16 +1931,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5723042</t>
+          <t xml:space="preserve">7162392</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F39">
-        <v>9166</v>
+        <v>468</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,16 +1981,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724047</t>
+          <t xml:space="preserve">740757, 7523861</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F40">
-        <v>820</v>
+        <v>467</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,16 +2031,16 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724388</t>
+          <t xml:space="preserve">741001, 5721394</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F41">
-        <v>448</v>
+        <v>610</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,16 +2081,16 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724388</t>
+          <t xml:space="preserve">741002, 7523861</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F42">
-        <v>1333</v>
+        <v>820</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,16 +2131,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">7162298</t>
+          <t xml:space="preserve">741003, 7523861</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F43">
-        <v>381</v>
+        <v>285</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2181,16 +2181,16 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">7162392</t>
+          <t xml:space="preserve">741003, 7523861</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F44">
-        <v>1657</v>
+        <v>294</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">7162392</t>
+          <t xml:space="preserve">741005, 5721571</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F45">
-        <v>468</v>
+        <v>788</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">740757, 7523861</t>
+          <t xml:space="preserve">741006, 5723518</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F46">
-        <v>467</v>
+        <v>612</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2331,16 +2331,16 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">740998, 5721389</t>
+          <t xml:space="preserve">741007, 5723600</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F47">
-        <v>786</v>
+        <v>735</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">741001, 5721394</t>
+          <t xml:space="preserve">741008, 5723618</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="F48">
-        <v>610</v>
+        <v>258</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2431,16 +2431,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">741002, 7523861</t>
+          <t xml:space="preserve">741056, 7776720</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F49">
-        <v>820</v>
+        <v>405</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2481,16 +2481,16 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">741003, 7523861</t>
+          <t xml:space="preserve">741056, 7776720</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F50">
-        <v>285</v>
+        <v>492</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2531,16 +2531,16 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">741003, 7523861</t>
+          <t xml:space="preserve">741060, 7523861</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F51">
-        <v>294</v>
+        <v>253</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2581,16 +2581,16 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">741005, 5721571</t>
+          <t xml:space="preserve">741079, 5721388</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F52">
-        <v>788</v>
+        <v>515</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2631,16 +2631,16 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">741006, 5723518</t>
+          <t xml:space="preserve">741180, 100756426</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F53">
-        <v>612</v>
+        <v>381</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2681,16 +2681,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">741007, 5723600</t>
+          <t xml:space="preserve">7925863</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F54">
-        <v>735</v>
+        <v>1406</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2731,16 +2731,16 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">741008, 5723618</t>
+          <t xml:space="preserve">7925863</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F55">
-        <v>258</v>
+        <v>3340</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2781,16 +2781,16 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">741033, 5006125</t>
+          <t xml:space="preserve">8216607</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F56">
-        <v>2198</v>
+        <v>892</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">741039, 5005508</t>
+          <t xml:space="preserve">8731154</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F57">
-        <v>2251</v>
+        <v>277</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2881,16 +2881,16 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">741044, 7523861</t>
+          <t xml:space="preserve">9913755</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">96</t>
         </is>
       </c>
       <c r="F58">
-        <v>363</v>
+        <v>300</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,30 +2931,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">741056, 7776720</t>
+          <t xml:space="preserve">5005525</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F59">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011417</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-13</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2981,30 +2981,30 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">741056, 7776720</t>
+          <t xml:space="preserve">5015548</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F60">
-        <v>492</v>
+        <v>1058</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200013710</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-05-14</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3031,30 +3031,30 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">741060, 7523861</t>
+          <t xml:space="preserve">5013631</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F61">
-        <v>253</v>
+        <v>1154</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200017365</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-10</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3081,30 +3081,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">741079, 5721388</t>
+          <t xml:space="preserve">5015548</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F62">
-        <v>515</v>
+        <v>1387</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200017403</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-10</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3131,30 +3131,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">741180, 100756426</t>
+          <t xml:space="preserve">5013631</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F63">
-        <v>381</v>
+        <v>513</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200017900</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-24</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3181,30 +3181,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">7919028</t>
+          <t xml:space="preserve">5015548</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F64">
-        <v>688</v>
+        <v>442</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200017902</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-24</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3231,30 +3231,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">7919028</t>
+          <t xml:space="preserve">5009238</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F65">
-        <v>801</v>
+        <v>1117</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200019667</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-08-31</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3281,30 +3281,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">7925863</t>
+          <t xml:space="preserve">5009238</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F66">
-        <v>1406</v>
+        <v>1239</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200020434</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3331,30 +3331,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">7925863</t>
+          <t xml:space="preserve">5721106</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F67">
-        <v>3340</v>
+        <v>1032</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200020428</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3381,30 +3381,30 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">8216607</t>
+          <t xml:space="preserve">5722864</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F68">
-        <v>892</v>
+        <v>620</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200020431</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">8731154</t>
+          <t xml:space="preserve">8521772</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3440,21 +3440,21 @@
         </is>
       </c>
       <c r="F69">
-        <v>277</v>
+        <v>1671</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200020471</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3481,30 +3481,30 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">9913755</t>
+          <t xml:space="preserve">8521772</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">96</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F70">
-        <v>300</v>
+        <v>366</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200020474</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5005525</t>
+          <t xml:space="preserve">8521772</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F71">
-        <v>418</v>
+        <v>1311</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011417</t>
+          <t xml:space="preserve">200020471</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-13</t>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5015548</t>
+          <t xml:space="preserve">8521772</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F72">
-        <v>1058</v>
+        <v>1505</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013710</t>
+          <t xml:space="preserve">200020471</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-14</t>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5015548</t>
+          <t xml:space="preserve">8521772</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F73">
-        <v>1387</v>
+        <v>1639</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017403</t>
+          <t xml:space="preserve">200020471</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-10</t>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5013631</t>
+          <t xml:space="preserve">8521772</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F74">
-        <v>513</v>
+        <v>888</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017900</t>
+          <t xml:space="preserve">200020471</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-24</t>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5015548</t>
+          <t xml:space="preserve">8521772</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F75">
-        <v>442</v>
+        <v>2117</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017902</t>
+          <t xml:space="preserve">200020471</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-24</t>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5009238</t>
+          <t xml:space="preserve">9733736</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3790,16 +3790,16 @@
         </is>
       </c>
       <c r="F76">
-        <v>1117</v>
+        <v>1961</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019667</t>
+          <t xml:space="preserve">200020860</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-31</t>
+          <t xml:space="preserve">2019-09-22</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,25 +3831,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5009238</t>
+          <t xml:space="preserve">5002967</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F77">
-        <v>1239</v>
+        <v>302</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020434</t>
+          <t xml:space="preserve">200021192</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-09-28</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721106</t>
+          <t xml:space="preserve">8521755</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3890,16 +3890,16 @@
         </is>
       </c>
       <c r="F78">
-        <v>1032</v>
+        <v>353</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020428</t>
+          <t xml:space="preserve">200021180</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-09-28</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,25 +3931,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5722864</t>
+          <t xml:space="preserve">5721743</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F79">
-        <v>620</v>
+        <v>1042</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020431</t>
+          <t xml:space="preserve">200021275</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-09-29</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">8521772</t>
+          <t xml:space="preserve">7084005</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3990,16 +3990,16 @@
         </is>
       </c>
       <c r="F80">
-        <v>1671</v>
+        <v>3453</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020471</t>
+          <t xml:space="preserve">200021511</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8521772</t>
+          <t xml:space="preserve">5008448</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F81">
-        <v>366</v>
+        <v>426</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020474</t>
+          <t xml:space="preserve">200022434</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-10-16</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,25 +4081,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">8521772</t>
+          <t xml:space="preserve">5723045</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F82">
-        <v>1311</v>
+        <v>1346</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020471</t>
+          <t xml:space="preserve">200022852</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-10-27</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,25 +4131,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">8521772</t>
+          <t xml:space="preserve">5723683</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F83">
-        <v>1505</v>
+        <v>1780</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020471</t>
+          <t xml:space="preserve">200023144</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-10-30</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">8521772</t>
+          <t xml:space="preserve">5010053</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F84">
-        <v>1639</v>
+        <v>525</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020471</t>
+          <t xml:space="preserve">200024094</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-11-17</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,25 +4231,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8521772</t>
+          <t xml:space="preserve">5010053</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F85">
-        <v>888</v>
+        <v>563</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020471</t>
+          <t xml:space="preserve">200024094</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-11-17</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">8521772</t>
+          <t xml:space="preserve">5010053</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F86">
-        <v>2117</v>
+        <v>1785</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020471</t>
+          <t xml:space="preserve">200024094</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-11-17</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">9733736</t>
+          <t xml:space="preserve">5720854</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="F87">
-        <v>1961</v>
+        <v>600</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020860</t>
+          <t xml:space="preserve">200024150</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-22</t>
+          <t xml:space="preserve">2019-11-18</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5002967</t>
+          <t xml:space="preserve">5009707</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4390,16 +4390,16 @@
         </is>
       </c>
       <c r="F88">
-        <v>302</v>
+        <v>428</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021192</t>
+          <t xml:space="preserve">200024461</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-28</t>
+          <t xml:space="preserve">2019-11-25</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">8521755</t>
+          <t xml:space="preserve">5723042</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4440,16 +4440,16 @@
         </is>
       </c>
       <c r="F89">
-        <v>353</v>
+        <v>9166</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021180</t>
+          <t xml:space="preserve">200025497</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-28</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721743</t>
+          <t xml:space="preserve">5721112</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="F90">
-        <v>1042</v>
+        <v>402</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021275</t>
+          <t xml:space="preserve">200025547</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-29</t>
+          <t xml:space="preserve">2019-12-16</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">7084005</t>
+          <t xml:space="preserve">5721214</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4540,16 +4540,16 @@
         </is>
       </c>
       <c r="F91">
-        <v>3453</v>
+        <v>290</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021511</t>
+          <t xml:space="preserve">200025548</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-30</t>
+          <t xml:space="preserve">2019-12-16</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4581,25 +4581,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5008448</t>
+          <t xml:space="preserve">5005634</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F92">
-        <v>426</v>
+        <v>885</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022434</t>
+          <t xml:space="preserve">200026062</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-16</t>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4631,25 +4631,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5723045</t>
+          <t xml:space="preserve">5005634</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F93">
-        <v>1346</v>
+        <v>560</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022852</t>
+          <t xml:space="preserve">200026065</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-27</t>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,25 +4681,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5723683</t>
+          <t xml:space="preserve">5005634</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F94">
-        <v>1780</v>
+        <v>560</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023144</t>
+          <t xml:space="preserve">200026065</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-30</t>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5010053</t>
+          <t xml:space="preserve">7162232</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4740,16 +4740,16 @@
         </is>
       </c>
       <c r="F95">
-        <v>525</v>
+        <v>464</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024094</t>
+          <t xml:space="preserve">200026073</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-17</t>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4781,25 +4781,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5010053</t>
+          <t xml:space="preserve">5723511</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F96">
-        <v>563</v>
+        <v>413</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024094</t>
+          <t xml:space="preserve">200026149</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-17</t>
+          <t xml:space="preserve">2019-12-23</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4831,25 +4831,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5010053</t>
+          <t xml:space="preserve">5724388</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F97">
-        <v>1785</v>
+        <v>296</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024094</t>
+          <t xml:space="preserve">200026233</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-17</t>
+          <t xml:space="preserve">2019-12-29</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,25 +4881,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5720854</t>
+          <t xml:space="preserve">7919028</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F98">
-        <v>600</v>
+        <v>688</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024150</t>
+          <t xml:space="preserve">100148052</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-18</t>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,25 +4931,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5009707</t>
+          <t xml:space="preserve">7919028</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F99">
-        <v>428</v>
+        <v>801</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024461</t>
+          <t xml:space="preserve">100148052</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-25</t>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721112</t>
+          <t xml:space="preserve">5721185</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4990,16 +4990,16 @@
         </is>
       </c>
       <c r="F100">
-        <v>402</v>
+        <v>768</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025547</t>
+          <t xml:space="preserve">200028193</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-16</t>
+          <t xml:space="preserve">2020-02-17</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5031,25 +5031,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721214</t>
+          <t xml:space="preserve">5004909</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F101">
-        <v>290</v>
+        <v>817</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025548</t>
+          <t xml:space="preserve">200028261</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-16</t>
+          <t xml:space="preserve">2020-02-19</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5081,25 +5081,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9441940</t>
+          <t xml:space="preserve">5004909</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F102">
-        <v>2246</v>
+        <v>4362</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025550</t>
+          <t xml:space="preserve">200028261</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-16</t>
+          <t xml:space="preserve">2020-02-19</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5005634</t>
+          <t xml:space="preserve">5004909</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F103">
-        <v>885</v>
+        <v>399</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026062</t>
+          <t xml:space="preserve">200028261</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2020-02-19</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5005634</t>
+          <t xml:space="preserve">9441940</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F104">
-        <v>560</v>
+        <v>2246</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026065</t>
+          <t xml:space="preserve">200028343</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2020-02-22</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,25 +5231,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5005634</t>
+          <t xml:space="preserve">5007601</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F105">
-        <v>560</v>
+        <v>5595</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026065</t>
+          <t xml:space="preserve">200036608</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2020-09-07</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,25 +5281,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">7162232</t>
+          <t xml:space="preserve">5007601</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F106">
-        <v>464</v>
+        <v>350</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026073</t>
+          <t xml:space="preserve">200036608</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2020-09-07</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5331,25 +5331,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5723511</t>
+          <t xml:space="preserve">5003564</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F107">
-        <v>413</v>
+        <v>512</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026149</t>
+          <t xml:space="preserve">200045772</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-23</t>
+          <t xml:space="preserve">2021-02-18</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724388</t>
+          <t xml:space="preserve">100061486</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5390,16 +5390,16 @@
         </is>
       </c>
       <c r="F108">
-        <v>296</v>
+        <v>745</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026233</t>
+          <t xml:space="preserve">311020719</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-29</t>
+          <t xml:space="preserve">2023-10-06</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5431,25 +5431,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721185</t>
+          <t xml:space="preserve">741033, 5006125</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F109">
-        <v>768</v>
+        <v>2198</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028193</t>
+          <t xml:space="preserve">311028311</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-17</t>
+          <t xml:space="preserve">2023-11-25</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5481,25 +5481,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">100061486</t>
+          <t xml:space="preserve">741039, 5005508</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F110">
-        <v>745</v>
+        <v>2251</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311020719</t>
+          <t xml:space="preserve">311028312</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-10-06</t>
+          <t xml:space="preserve">2023-11-25</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">338462, 338463</t>
+          <t xml:space="preserve">5721110</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5540,16 +5540,16 @@
         </is>
       </c>
       <c r="F111">
-        <v>2225</v>
+        <v>734</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311049395</t>
+          <t xml:space="preserve">311069753</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-04-16</t>
+          <t xml:space="preserve">2024-08-22</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5586,11 +5586,11 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F112">
-        <v>734</v>
+        <v>1471</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -5636,11 +5636,11 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F113">
-        <v>1471</v>
+        <v>568</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -5686,11 +5686,11 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F114">
-        <v>568</v>
+        <v>927</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -5736,11 +5736,11 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F115">
-        <v>927</v>
+        <v>581</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -5781,25 +5781,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721110</t>
+          <t xml:space="preserve">740998, 5721389</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F116">
-        <v>581</v>
+        <v>786</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311069753</t>
+          <t xml:space="preserve">311192944</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-08-22</t>
+          <t xml:space="preserve">2026-08-04</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,25 +5831,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">500693, 7523861</t>
+          <t xml:space="preserve">741044, 7523861</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F117">
-        <v>3059</v>
+        <v>363</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311637293</t>
+          <t xml:space="preserve">311312790</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-21</t>
+          <t xml:space="preserve">2028-05-08</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,25 +5881,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">100366309</t>
+          <t xml:space="preserve">500693, 7523861</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F118">
-        <v>1232</v>
+        <v>3059</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311641855</t>
+          <t xml:space="preserve">311637293</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-10</t>
+          <t xml:space="preserve">2032-10-21</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5931,25 +5931,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">338409, 338410, 338411</t>
+          <t xml:space="preserve">100366309</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F119">
-        <v>1180</v>
+        <v>1232</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664174</t>
+          <t xml:space="preserve">311641855</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-04</t>
+          <t xml:space="preserve">2032-11-10</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">

--- a/public/exports/29189935.xlsx
+++ b/public/exports/29189935.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:L119"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhusgade 1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">100013068</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>1571</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pillevej 2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">100014836</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>1221</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tuskærvej 9</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">100086746</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>615</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kystcentervej 11</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7680</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">100756424</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>297</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kystcentervej 11</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7680</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">100756424</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>447</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kystcentervej 1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7680</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">100756426</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">37</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>732</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndergade 2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">338409, 338410, 338411</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>1180</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ågade 14</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">338462, 338463</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>2225</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Algade 92</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">5006098</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>2781</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Algade 36</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">5006098</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>782</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Algade 36</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">5006098</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>1499</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bøgelundvej 50</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">5006203</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>625</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bøgelundvej 50</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">5006203</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>721</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fabjergstad 31B</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">5009707</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>397</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fabjergstad 31C</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">5009707</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>598</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fabjergstad 31D</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">5009707</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>850</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevænget 11</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">5015548</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>943</v>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevænget 11</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">5015548</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>585</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevænget 11</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">5015548</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>1088</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevænget 11</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">5015548</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">20</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>1108</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevænget 11</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">5015548</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>1444</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevænget 11</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">5015548</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>311</v>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rom Skole 12</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">5017120</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>1031</v>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østergade 10</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">5721212</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>744</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhusgade 2</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">5721227</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>4652</v>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nygade 35</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">5721713</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>757</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nygade 18</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">5721809</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>2380</v>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nygade 16</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">5721924</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>348</v>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thøger Larsens Vej 5</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">5721924</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>351</v>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vangevej 10</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">5722450</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>300</v>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vangevej 12A</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">5722450</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>300</v>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vangevej 12B</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">5722450</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>300</v>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nissumvej 8</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">5724047</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>820</v>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nissumvej 34</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">5724388</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>448</v>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nissumvej 34</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">5724388</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>1333</v>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østergade 14</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">7162298</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>381</v>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østergade 50</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">7162392</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>1657</v>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østergade 50</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">7162392</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>468</v>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnen 54</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">740757, 7523861</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>467</v>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnen 36</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">741001, 5721394</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>610</v>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnen 72</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">741002, 7523861</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>820</v>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnen 93</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">741003, 7523861</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">24</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>285</v>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnen 95A</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">741003, 7523861</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">25</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>294</v>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vesterled 2</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">741005, 5721571</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>788</v>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østergade 63</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">741006, 5723518</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>612</v>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandvejen 24</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">741007, 5723600</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>735</v>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vinkelhagevej 10B</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">741008, 5723618</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>258</v>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandvejen 15</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">741056, 7776720</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>405</v>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandvejen 15</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">741056, 7776720</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>492</v>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnen 68</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">741060, 7523861</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>253</v>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnen 23</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">741079, 5721388</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>515</v>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I52" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kystcentervej 1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7680</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">741180, 100756426</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">21</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>381</v>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I53" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nygade 4</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">7925863</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>1406</v>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I54" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2731,33 +3271,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nygade 6</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">7925863</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>3340</v>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I55" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2781,33 +3331,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærøvej 17</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7680</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">8216607</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>892</v>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I56" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2831,33 +3391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søhusvænget 8</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7660</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">8731154</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>277</v>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I57" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2881,33 +3451,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrivej 49E</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">9913755</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">96</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>300</v>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I58" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2931,33 +3511,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nejrupvej 6B</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">5005525</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>418</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">200011417</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-03-13</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2981,33 +3571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevænget 11</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">5015548</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>1058</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">200013710</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-05-14</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3031,33 +3631,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lomborgvej 84</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">5013631</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>1154</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">200017365</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-07-10</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3081,33 +3691,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevænget 3</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">5015548</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>1387</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">200017403</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-07-10</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3131,33 +3751,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lomborgvej 80</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">5013631</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>513</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">200017900</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-07-24</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3181,33 +3811,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevænget 17</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">5015548</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>442</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">200017902</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-07-24</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3231,33 +3871,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tangsøgade 67</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7650</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">5009238</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>1117</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">200019667</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-08-31</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3281,33 +3931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tangsøgade 67</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7650</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">5009238</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>1239</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">200020434</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3331,33 +3991,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 3</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">5721106</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>1032</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">200020428</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3381,33 +4051,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østerbrogade 3A</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">5722864</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>620</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">200020431</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3431,33 +4111,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nissumvej 10</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">8521772</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>1671</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">200020471</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3481,33 +4171,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nissumvej 10</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">8521772</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>366</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">200020474</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3531,33 +4231,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nissumvej 10</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">8521772</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F71">
+      <c r="H71">
         <v>1311</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">200020471</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3581,33 +4291,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nissumvej 10</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">8521772</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F72">
+      <c r="H72">
         <v>1505</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">200020471</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3631,33 +4351,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nissumvej 10</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">8521772</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F73">
+      <c r="H73">
         <v>1639</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">200020471</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3681,33 +4411,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nissumvej 10</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">8521772</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="H74">
         <v>888</v>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">200020471</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3731,33 +4471,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nissumvej 10</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">8521772</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F75">
+      <c r="H75">
         <v>2117</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">200020471</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3781,33 +4531,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vesterhavsgade 164</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7680</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">9733736</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F76">
+      <c r="H76">
         <v>1961</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">200020860</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-22</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3831,33 +4591,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndergade 1B</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7673</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">5002967</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>302</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">200021192</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-28</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3881,33 +4651,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 33</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">8521755</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>353</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">200021180</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-28</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3931,33 +4711,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nygade 3</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">5721743</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F79">
+      <c r="H79">
         <v>1042</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">200021275</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-29</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3981,33 +4771,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrivej 49</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">7084005</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>3453</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">200021511</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4031,33 +4831,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærøvej 79A</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7680</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">5008448</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F81">
+      <c r="H81">
         <v>426</v>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">200022434</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-10-16</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4081,33 +4891,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 7</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">5723045</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="H82">
         <v>1346</v>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">200022852</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-10-27</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4131,33 +4951,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrivej 43</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t xml:space="preserve">5723683</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F83">
+      <c r="H83">
         <v>1780</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">200023144</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-10-30</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4181,33 +5011,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brogade 67</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7660</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t xml:space="preserve">5010053</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F84">
+      <c r="H84">
         <v>525</v>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">200024094</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-11-17</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4231,33 +5071,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brogade 67</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7660</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t xml:space="preserve">5010053</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F85">
+      <c r="H85">
         <v>563</v>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t xml:space="preserve">200024094</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-11-17</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4281,33 +5131,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brogade 67</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7660</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t xml:space="preserve">5010053</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F86">
+      <c r="H86">
         <v>1785</v>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">200024094</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-11-17</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4331,33 +5191,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnegade 14</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t xml:space="preserve">5720854</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F87">
+      <c r="H87">
         <v>600</v>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">200024150</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-11-18</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4381,33 +5251,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fabjergstad 31A</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t xml:space="preserve">5009707</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F88">
+      <c r="H88">
         <v>428</v>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t xml:space="preserve">200024461</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-11-25</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4431,33 +5311,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Christinelystvej 3</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t xml:space="preserve">5723042</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F89">
+      <c r="H89">
         <v>9166</v>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200025497</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
+      <c r="I89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200025503</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4481,33 +5371,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vasen 10</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t xml:space="preserve">5721112</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F90">
+      <c r="H90">
         <v>402</v>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">200025547</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-12-16</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4531,33 +5431,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhusvænget 6</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t xml:space="preserve">5721214</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F91">
+      <c r="H91">
         <v>290</v>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t xml:space="preserve">200025548</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-12-16</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4581,33 +5491,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Klinkbyvænget 1</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t xml:space="preserve">5005634</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F92">
+      <c r="H92">
         <v>885</v>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t xml:space="preserve">200026062</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4631,33 +5551,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Klinkbyvænget 2</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t xml:space="preserve">5005634</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F93">
+      <c r="H93">
         <v>560</v>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t xml:space="preserve">200026065</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4681,33 +5611,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Klinkbyvænget 3</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t xml:space="preserve">5005634</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F94">
+      <c r="H94">
         <v>560</v>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t xml:space="preserve">200026065</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4731,33 +5671,43 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Klinkbyvænget 5</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t xml:space="preserve">7162232</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F95">
+      <c r="H95">
         <v>464</v>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t xml:space="preserve">200026073</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4781,33 +5731,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østergade 67</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t xml:space="preserve">5723511</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F96">
+      <c r="H96">
         <v>413</v>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t xml:space="preserve">200026149</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-12-23</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4831,33 +5791,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nissumvej 34</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t xml:space="preserve">5724388</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F97">
+      <c r="H97">
         <v>296</v>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t xml:space="preserve">200026233</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-12-29</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4881,33 +5851,43 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fårevej 145</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7650</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t xml:space="preserve">7919028</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F98">
+      <c r="H98">
         <v>688</v>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t xml:space="preserve">100148052</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4931,33 +5911,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fårevej 143</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7650</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t xml:space="preserve">7919028</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F99">
+      <c r="H99">
         <v>801</v>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t xml:space="preserve">100148052</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4981,33 +5971,43 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bredgade 17</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t xml:space="preserve">5721185</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F100">
+      <c r="H100">
         <v>768</v>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t xml:space="preserve">200028193</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-02-17</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5031,33 +6031,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 10</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7673</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t xml:space="preserve">5004909</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>817</v>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t xml:space="preserve">200028261</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-02-19</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5081,33 +6091,43 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 8</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7673</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t xml:space="preserve">5004909</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F102">
+      <c r="H102">
         <v>4362</v>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t xml:space="preserve">200028261</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-02-19</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="K102" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5131,33 +6151,43 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 8</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7673</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t xml:space="preserve">5004909</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F103">
+      <c r="H103">
         <v>399</v>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t xml:space="preserve">200028261</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-02-19</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5181,33 +6211,43 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndergade 1</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7673</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t xml:space="preserve">9441940</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F104">
+      <c r="H104">
         <v>2246</v>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t xml:space="preserve">200028343</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-02-22</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5231,33 +6271,43 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 7</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7680</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t xml:space="preserve">5007601</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F105">
+      <c r="H105">
         <v>5595</v>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t xml:space="preserve">200036608</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-09-07</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5281,33 +6331,43 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 7</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7680</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t xml:space="preserve">5007601</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F106">
+      <c r="H106">
         <v>350</v>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t xml:space="preserve">200036608</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-09-07</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5331,33 +6391,43 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrivej 14</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7673</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t xml:space="preserve">5003564</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F107">
+      <c r="H107">
         <v>512</v>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t xml:space="preserve">200045772</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-02-18</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5381,33 +6451,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Solvangen 20</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7660</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
           <t xml:space="preserve">100061486</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F108">
+      <c r="H108">
         <v>745</v>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="I108" t="inlineStr">
         <is>
           <t xml:space="preserve">311020719</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t xml:space="preserve">2023-10-06</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="K108" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5431,33 +6511,43 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rammegårdvej 8</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t xml:space="preserve">741033, 5006125</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F109">
+      <c r="H109">
         <v>2198</v>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t xml:space="preserve">311028311</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t xml:space="preserve">2023-11-25</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5481,33 +6571,43 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nejrupvej 2C</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t xml:space="preserve">741039, 5005508</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F110">
+      <c r="H110">
         <v>2251</v>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t xml:space="preserve">311028312</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t xml:space="preserve">2023-11-25</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5531,33 +6631,43 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vasen 14</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
           <t xml:space="preserve">5721110</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F111">
+      <c r="H111">
         <v>734</v>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t xml:space="preserve">311069753</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-08-22</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="K111" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5581,33 +6691,43 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vasen 14</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
           <t xml:space="preserve">5721110</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F112">
+      <c r="H112">
         <v>1471</v>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t xml:space="preserve">311069753</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-08-22</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="K112" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5631,33 +6751,43 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vasen 14</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
           <t xml:space="preserve">5721110</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F113">
+      <c r="H113">
         <v>568</v>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t xml:space="preserve">311069753</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-08-22</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="K113" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5681,33 +6811,43 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vasen 14</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
           <t xml:space="preserve">5721110</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F114">
+      <c r="H114">
         <v>927</v>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t xml:space="preserve">311069753</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-08-22</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="K114" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5731,33 +6871,43 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vasen 14</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
           <t xml:space="preserve">5721110</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F115">
+      <c r="H115">
         <v>581</v>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t xml:space="preserve">311069753</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="J115" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-08-22</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="K115" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5781,33 +6931,43 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnen 18</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
           <t xml:space="preserve">740998, 5721389</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F116">
+      <c r="H116">
         <v>786</v>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="I116" t="inlineStr">
         <is>
           <t xml:space="preserve">311192944</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="J116" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-04</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="K116" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5831,33 +6991,43 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnen 92</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
           <t xml:space="preserve">741044, 7523861</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F117">
+      <c r="H117">
         <v>363</v>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t xml:space="preserve">311312790</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-05-08</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="K117" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5881,33 +7051,43 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnen 62</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t xml:space="preserve">500693, 7523861</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F118">
+      <c r="H118">
         <v>3059</v>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="I118" t="inlineStr">
         <is>
           <t xml:space="preserve">311637293</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="J118" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-10-21</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="K118" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5931,39 +7111,49 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østergade 32</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7620</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
           <t xml:space="preserve">100366309</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F119">
+      <c r="H119">
         <v>1232</v>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t xml:space="preserve">311641855</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="J119" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-10</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="K119" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J119"/>
+  <autoFilter ref="A1:L119"/>
 </worksheet>
 </file>
--- a/public/exports/29189935.xlsx
+++ b/public/exports/29189935.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 1</t>
+          <t xml:space="preserve">Algade 36</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,16 +101,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100013068</t>
+          <t xml:space="preserve">5006098</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H2">
-        <v>1571</v>
+        <v>782</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pillevej 2</t>
+          <t xml:space="preserve">Algade 36</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100014836</t>
+          <t xml:space="preserve">5006098</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H3">
-        <v>1221</v>
+        <v>1499</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuskærvej 9</t>
+          <t xml:space="preserve">Algade 92</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,16 +221,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100086746</t>
+          <t xml:space="preserve">5006098</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H4">
-        <v>615</v>
+        <v>2781</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kystcentervej 11</t>
+          <t xml:space="preserve">Bøgelundvej 50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">7680</t>
+          <t xml:space="preserve">7620</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">100756424</t>
+          <t xml:space="preserve">5006203</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H5">
-        <v>297</v>
+        <v>625</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,26 +331,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kystcentervej 11</t>
+          <t xml:space="preserve">Bøgelundvej 50</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">7680</t>
+          <t xml:space="preserve">7620</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">100756424</t>
+          <t xml:space="preserve">5006203</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H6">
-        <v>447</v>
+        <v>721</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kystcentervej 1</t>
+          <t xml:space="preserve">Fabjergstad 31B</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">7680</t>
+          <t xml:space="preserve">7620</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">100756426</t>
+          <t xml:space="preserve">5009707</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H7">
-        <v>732</v>
+        <v>397</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 2</t>
+          <t xml:space="preserve">Fabjergstad 31C</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,16 +461,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">338409, 338410, 338411</t>
+          <t xml:space="preserve">5009707</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H8">
-        <v>1180</v>
+        <v>598</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågade 14</t>
+          <t xml:space="preserve">Fabjergstad 31D</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -521,16 +521,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">338462, 338463</t>
+          <t xml:space="preserve">5009707</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H9">
-        <v>2225</v>
+        <v>850</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Algade 92</t>
+          <t xml:space="preserve">Havnen 23</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5006098</t>
+          <t xml:space="preserve">741079, 5721388</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H10">
-        <v>2781</v>
+        <v>515</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Algade 36</t>
+          <t xml:space="preserve">Havnen 36</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5006098</t>
+          <t xml:space="preserve">741001, 5721394</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H11">
-        <v>782</v>
+        <v>610</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Algade 36</t>
+          <t xml:space="preserve">Havnen 54</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5006098</t>
+          <t xml:space="preserve">740757, 7523861</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H12">
-        <v>1499</v>
+        <v>467</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgelundvej 50</t>
+          <t xml:space="preserve">Havnen 68</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,16 +761,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5006203</t>
+          <t xml:space="preserve">741060, 7523861</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H13">
-        <v>625</v>
+        <v>253</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgelundvej 50</t>
+          <t xml:space="preserve">Havnen 72</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,16 +821,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5006203</t>
+          <t xml:space="preserve">741002, 7523861</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H14">
-        <v>721</v>
+        <v>820</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabjergstad 31B</t>
+          <t xml:space="preserve">Havnen 93</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -881,16 +881,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5009707</t>
+          <t xml:space="preserve">741003, 7523861</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H15">
-        <v>397</v>
+        <v>285</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabjergstad 31C</t>
+          <t xml:space="preserve">Havnen 95A</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,16 +941,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5009707</t>
+          <t xml:space="preserve">741003, 7523861</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="H16">
-        <v>598</v>
+        <v>294</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabjergstad 31D</t>
+          <t xml:space="preserve">Industrivej 49E</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1001,16 +1001,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5009707</t>
+          <t xml:space="preserve">9913755</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">96</t>
         </is>
       </c>
       <c r="H17">
-        <v>850</v>
+        <v>300</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,26 +1051,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 11</t>
+          <t xml:space="preserve">Kystcentervej 1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">7620</t>
+          <t xml:space="preserve">7680</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5015548</t>
+          <t xml:space="preserve">100756426</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="H18">
-        <v>943</v>
+        <v>732</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,26 +1111,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 11</t>
+          <t xml:space="preserve">Kystcentervej 1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7620</t>
+          <t xml:space="preserve">7680</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5015548</t>
+          <t xml:space="preserve">741180, 100756426</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H19">
-        <v>585</v>
+        <v>381</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 11</t>
+          <t xml:space="preserve">Kystcentervej 11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">7620</t>
+          <t xml:space="preserve">7680</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5015548</t>
+          <t xml:space="preserve">100756424</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H20">
-        <v>1088</v>
+        <v>297</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,26 +1231,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 11</t>
+          <t xml:space="preserve">Kystcentervej 11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">7620</t>
+          <t xml:space="preserve">7680</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5015548</t>
+          <t xml:space="preserve">100756424</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H21">
-        <v>1108</v>
+        <v>447</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 11</t>
+          <t xml:space="preserve">Nissumvej 34</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,16 +1301,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5015548</t>
+          <t xml:space="preserve">5724388</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H22">
-        <v>1444</v>
+        <v>448</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 11</t>
+          <t xml:space="preserve">Nissumvej 34</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,16 +1361,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5015548</t>
+          <t xml:space="preserve">5724388</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H23">
-        <v>311</v>
+        <v>1333</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rom Skole 12</t>
+          <t xml:space="preserve">Nissumvej 8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5017120</t>
+          <t xml:space="preserve">5724047</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="H24">
-        <v>1031</v>
+        <v>820</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 10</t>
+          <t xml:space="preserve">Nygade 16</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721212</t>
+          <t xml:space="preserve">5721924</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="H25">
-        <v>744</v>
+        <v>348</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 2</t>
+          <t xml:space="preserve">Nygade 18</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1541,16 +1541,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721227</t>
+          <t xml:space="preserve">5721809</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H26">
-        <v>4652</v>
+        <v>2380</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 18</t>
+          <t xml:space="preserve">Nygade 4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,16 +1661,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721809</t>
+          <t xml:space="preserve">7925863</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H28">
-        <v>2380</v>
+        <v>1406</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 16</t>
+          <t xml:space="preserve">Nygade 6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,16 +1721,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721924</t>
+          <t xml:space="preserve">7925863</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H29">
-        <v>348</v>
+        <v>3340</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thøger Larsens Vej 5</t>
+          <t xml:space="preserve">Pillevej 2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,16 +1781,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721924</t>
+          <t xml:space="preserve">100014836</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H30">
-        <v>351</v>
+        <v>1221</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vangevej 10</t>
+          <t xml:space="preserve">Rom Skole 12</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5722450</t>
+          <t xml:space="preserve">5017120</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="H31">
-        <v>300</v>
+        <v>1031</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vangevej 12A</t>
+          <t xml:space="preserve">Rådhusgade 1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,16 +1901,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5722450</t>
+          <t xml:space="preserve">100013068</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H32">
-        <v>300</v>
+        <v>1571</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vangevej 12B</t>
+          <t xml:space="preserve">Rådhusgade 2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1961,16 +1961,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5722450</t>
+          <t xml:space="preserve">5721227</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H33">
-        <v>300</v>
+        <v>4652</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nissumvej 8</t>
+          <t xml:space="preserve">Skolevænget 11</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,16 +2021,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724047</t>
+          <t xml:space="preserve">5015548</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H34">
-        <v>820</v>
+        <v>943</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nissumvej 34</t>
+          <t xml:space="preserve">Skolevænget 11</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2081,16 +2081,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724388</t>
+          <t xml:space="preserve">5015548</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H35">
-        <v>448</v>
+        <v>585</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nissumvej 34</t>
+          <t xml:space="preserve">Skolevænget 11</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,16 +2141,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724388</t>
+          <t xml:space="preserve">5015548</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H36">
-        <v>1333</v>
+        <v>1088</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 14</t>
+          <t xml:space="preserve">Skolevænget 11</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2201,16 +2201,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">7162298</t>
+          <t xml:space="preserve">5015548</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H37">
-        <v>381</v>
+        <v>1108</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 50</t>
+          <t xml:space="preserve">Skolevænget 11</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2261,16 +2261,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">7162392</t>
+          <t xml:space="preserve">5015548</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H38">
-        <v>1657</v>
+        <v>1444</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 50</t>
+          <t xml:space="preserve">Skolevænget 11</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2321,16 +2321,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">7162392</t>
+          <t xml:space="preserve">5015548</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H39">
-        <v>468</v>
+        <v>311</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 54</t>
+          <t xml:space="preserve">Strandvejen 15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2381,16 +2381,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">740757, 7523861</t>
+          <t xml:space="preserve">741056, 7776720</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H40">
-        <v>467</v>
+        <v>405</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 36</t>
+          <t xml:space="preserve">Strandvejen 15</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2441,16 +2441,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">741001, 5721394</t>
+          <t xml:space="preserve">741056, 7776720</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H41">
-        <v>610</v>
+        <v>492</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 72</t>
+          <t xml:space="preserve">Strandvejen 24</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,16 +2501,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">741002, 7523861</t>
+          <t xml:space="preserve">741007, 5723600</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H42">
-        <v>820</v>
+        <v>735</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2551,26 +2551,26 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 93</t>
+          <t xml:space="preserve">Søhusvænget 8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">7620</t>
+          <t xml:space="preserve">7660</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">741003, 7523861</t>
+          <t xml:space="preserve">8731154</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 95A</t>
+          <t xml:space="preserve">Thøger Larsens Vej 5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,16 +2621,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">741003, 7523861</t>
+          <t xml:space="preserve">5721924</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H44">
-        <v>294</v>
+        <v>351</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterled 2</t>
+          <t xml:space="preserve">Tuskærvej 9</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">741005, 5721571</t>
+          <t xml:space="preserve">100086746</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="H45">
-        <v>788</v>
+        <v>615</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 63</t>
+          <t xml:space="preserve">Vangevej 10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">741006, 5723518</t>
+          <t xml:space="preserve">5722450</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="H46">
-        <v>612</v>
+        <v>300</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 24</t>
+          <t xml:space="preserve">Vangevej 12A</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2801,16 +2801,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">741007, 5723600</t>
+          <t xml:space="preserve">5722450</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H47">
-        <v>735</v>
+        <v>300</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelhagevej 10B</t>
+          <t xml:space="preserve">Vangevej 12B</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2861,16 +2861,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">741008, 5723618</t>
+          <t xml:space="preserve">5722450</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H48">
-        <v>258</v>
+        <v>300</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 15</t>
+          <t xml:space="preserve">Vesterled 2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2921,16 +2921,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">741056, 7776720</t>
+          <t xml:space="preserve">741005, 5721571</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H49">
-        <v>405</v>
+        <v>788</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 15</t>
+          <t xml:space="preserve">Vinkelhagevej 10B</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2981,16 +2981,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">741056, 7776720</t>
+          <t xml:space="preserve">741008, 5723618</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H50">
-        <v>492</v>
+        <v>258</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3031,26 +3031,26 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 68</t>
+          <t xml:space="preserve">Ærøvej 17</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7620</t>
+          <t xml:space="preserve">7680</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">741060, 7523861</t>
+          <t xml:space="preserve">8216607</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H51">
-        <v>253</v>
+        <v>892</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 23</t>
+          <t xml:space="preserve">Østergade 10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3101,16 +3101,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">741079, 5721388</t>
+          <t xml:space="preserve">5721212</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H52">
-        <v>515</v>
+        <v>744</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3151,22 +3151,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kystcentervej 1</t>
+          <t xml:space="preserve">Østergade 14</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">7680</t>
+          <t xml:space="preserve">7620</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">741180, 100756426</t>
+          <t xml:space="preserve">7162298</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H53">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 4</t>
+          <t xml:space="preserve">Østergade 50</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7925863</t>
+          <t xml:space="preserve">7162392</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="H54">
-        <v>1406</v>
+        <v>1657</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 6</t>
+          <t xml:space="preserve">Østergade 50</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3281,16 +3281,16 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7925863</t>
+          <t xml:space="preserve">7162392</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H55">
-        <v>3340</v>
+        <v>468</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3331,17 +3331,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ærøvej 17</t>
+          <t xml:space="preserve">Østergade 63</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7680</t>
+          <t xml:space="preserve">7620</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">8216607</t>
+          <t xml:space="preserve">741006, 5723518</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="H56">
-        <v>892</v>
+        <v>612</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3391,40 +3391,40 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søhusvænget 8</t>
+          <t xml:space="preserve">Nejrupvej 6B</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">7660</t>
+          <t xml:space="preserve">7620</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">8731154</t>
+          <t xml:space="preserve">5005525</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H57">
-        <v>277</v>
+        <v>418</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011417</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-13</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 49E</t>
+          <t xml:space="preserve">Skolevænget 11</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,30 +3461,30 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">9913755</t>
+          <t xml:space="preserve">5015548</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">96</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H58">
-        <v>300</v>
+        <v>1058</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200013710</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-05-14</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nejrupvej 6B</t>
+          <t xml:space="preserve">Lomborgvej 84</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3521,25 +3521,25 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5005525</t>
+          <t xml:space="preserve">5013631</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H59">
-        <v>418</v>
+        <v>1154</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011417</t>
+          <t xml:space="preserve">200017418</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-13</t>
+          <t xml:space="preserve">2019-07-10</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 11</t>
+          <t xml:space="preserve">Skolevænget 3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3586,20 +3586,20 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H60">
-        <v>1058</v>
+        <v>1387</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013710</t>
+          <t xml:space="preserve">200017403</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-14</t>
+          <t xml:space="preserve">2019-07-10</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lomborgvej 84</t>
+          <t xml:space="preserve">Lomborgvej 80</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3646,20 +3646,20 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H61">
-        <v>1154</v>
+        <v>513</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017365</t>
+          <t xml:space="preserve">200017900</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-10</t>
+          <t xml:space="preserve">2019-07-24</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 3</t>
+          <t xml:space="preserve">Skolevænget 17</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3706,20 +3706,20 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H62">
-        <v>1387</v>
+        <v>442</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017403</t>
+          <t xml:space="preserve">200017902</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-10</t>
+          <t xml:space="preserve">2019-07-24</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,35 +3751,35 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lomborgvej 80</t>
+          <t xml:space="preserve">Tangsøgade 67</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">7620</t>
+          <t xml:space="preserve">7650</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5013631</t>
+          <t xml:space="preserve">5009238</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H63">
-        <v>513</v>
+        <v>1117</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017900</t>
+          <t xml:space="preserve">200019667</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-24</t>
+          <t xml:space="preserve">2019-08-31</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 17</t>
+          <t xml:space="preserve">Nissumvej 10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3821,25 +3821,25 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5015548</t>
+          <t xml:space="preserve">8521772</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H64">
-        <v>442</v>
+        <v>1671</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017902</t>
+          <t xml:space="preserve">200020471</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-24</t>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,35 +3871,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangsøgade 67</t>
+          <t xml:space="preserve">Nissumvej 10</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">7650</t>
+          <t xml:space="preserve">7620</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5009238</t>
+          <t xml:space="preserve">8521772</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H65">
-        <v>1117</v>
+        <v>366</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019667</t>
+          <t xml:space="preserve">200020474</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-31</t>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3931,17 +3931,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangsøgade 67</t>
+          <t xml:space="preserve">Nissumvej 10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">7650</t>
+          <t xml:space="preserve">7620</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5009238</t>
+          <t xml:space="preserve">8521772</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3950,11 +3950,11 @@
         </is>
       </c>
       <c r="H66">
-        <v>1239</v>
+        <v>1311</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020434</t>
+          <t xml:space="preserve">200020471</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3</t>
+          <t xml:space="preserve">Nissumvej 10</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4001,20 +4001,20 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721106</t>
+          <t xml:space="preserve">8521772</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H67">
-        <v>1032</v>
+        <v>1505</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020428</t>
+          <t xml:space="preserve">200020471</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østerbrogade 3A</t>
+          <t xml:space="preserve">Nissumvej 10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4061,20 +4061,20 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5722864</t>
+          <t xml:space="preserve">8521772</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H68">
-        <v>620</v>
+        <v>1639</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020431</t>
+          <t xml:space="preserve">200020471</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4126,11 +4126,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H69">
-        <v>1671</v>
+        <v>888</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -4186,15 +4186,15 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H70">
-        <v>366</v>
+        <v>2117</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020474</t>
+          <t xml:space="preserve">200020471</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nissumvej 10</t>
+          <t xml:space="preserve">Skolegade 3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4241,20 +4241,20 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">8521772</t>
+          <t xml:space="preserve">5721106</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H71">
-        <v>1311</v>
+        <v>1032</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020471</t>
+          <t xml:space="preserve">200020428</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4291,30 +4291,30 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nissumvej 10</t>
+          <t xml:space="preserve">Tangsøgade 67</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">7620</t>
+          <t xml:space="preserve">7650</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">8521772</t>
+          <t xml:space="preserve">5009238</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H72">
-        <v>1505</v>
+        <v>1239</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020471</t>
+          <t xml:space="preserve">200020434</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nissumvej 10</t>
+          <t xml:space="preserve">Østerbrogade 3A</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4361,20 +4361,20 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">8521772</t>
+          <t xml:space="preserve">5722864</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H73">
-        <v>1639</v>
+        <v>620</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020471</t>
+          <t xml:space="preserve">200020431</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4411,35 +4411,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nissumvej 10</t>
+          <t xml:space="preserve">Vesterhavsgade 164</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">7620</t>
+          <t xml:space="preserve">7680</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">8521772</t>
+          <t xml:space="preserve">9733736</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H74">
-        <v>888</v>
+        <v>1961</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020471</t>
+          <t xml:space="preserve">200020860</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-09-22</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nissumvej 10</t>
+          <t xml:space="preserve">Skolevej 33</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">8521772</t>
+          <t xml:space="preserve">8521755</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H75">
-        <v>2117</v>
+        <v>353</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020471</t>
+          <t xml:space="preserve">200021180</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-09-28</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,17 +4531,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterhavsgade 164</t>
+          <t xml:space="preserve">Søndergade 1B</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7680</t>
+          <t xml:space="preserve">7673</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9733736</t>
+          <t xml:space="preserve">5002967</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4550,16 +4550,16 @@
         </is>
       </c>
       <c r="H76">
-        <v>1961</v>
+        <v>302</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020860</t>
+          <t xml:space="preserve">200021192</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-22</t>
+          <t xml:space="preserve">2019-09-28</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 1B</t>
+          <t xml:space="preserve">Nygade 3</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">7673</t>
+          <t xml:space="preserve">7620</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5002967</t>
+          <t xml:space="preserve">5721743</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4610,16 +4610,16 @@
         </is>
       </c>
       <c r="H77">
-        <v>302</v>
+        <v>1042</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021192</t>
+          <t xml:space="preserve">200021275</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-28</t>
+          <t xml:space="preserve">2019-09-29</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 33</t>
+          <t xml:space="preserve">Industrivej 49</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">8521755</t>
+          <t xml:space="preserve">7084005</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4670,16 +4670,16 @@
         </is>
       </c>
       <c r="H78">
-        <v>353</v>
+        <v>3453</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021180</t>
+          <t xml:space="preserve">200021511</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-28</t>
+          <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 3</t>
+          <t xml:space="preserve">Ærøvej 79A</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">7620</t>
+          <t xml:space="preserve">7680</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721743</t>
+          <t xml:space="preserve">5008448</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4730,16 +4730,16 @@
         </is>
       </c>
       <c r="H79">
-        <v>1042</v>
+        <v>426</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021275</t>
+          <t xml:space="preserve">200022434</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-29</t>
+          <t xml:space="preserve">2019-10-16</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 49</t>
+          <t xml:space="preserve">Skolevej 7</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">7084005</t>
+          <t xml:space="preserve">5723045</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4790,16 +4790,16 @@
         </is>
       </c>
       <c r="H80">
-        <v>3453</v>
+        <v>1346</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021511</t>
+          <t xml:space="preserve">200022852</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-30</t>
+          <t xml:space="preserve">2019-10-27</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4831,17 +4831,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ærøvej 79A</t>
+          <t xml:space="preserve">Industrivej 43</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">7680</t>
+          <t xml:space="preserve">7620</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5008448</t>
+          <t xml:space="preserve">5723683</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="H81">
-        <v>426</v>
+        <v>1780</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022434</t>
+          <t xml:space="preserve">200023144</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-16</t>
+          <t xml:space="preserve">2019-10-30</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 7</t>
+          <t xml:space="preserve">Brogade 67</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">7620</t>
+          <t xml:space="preserve">7660</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5723045</t>
+          <t xml:space="preserve">5010053</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="H82">
-        <v>1346</v>
+        <v>525</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022852</t>
+          <t xml:space="preserve">200024094</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-27</t>
+          <t xml:space="preserve">2019-11-17</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4951,35 +4951,35 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 43</t>
+          <t xml:space="preserve">Brogade 67</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">7620</t>
+          <t xml:space="preserve">7660</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5723683</t>
+          <t xml:space="preserve">5010053</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H83">
-        <v>1780</v>
+        <v>563</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023144</t>
+          <t xml:space="preserve">200024094</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-30</t>
+          <t xml:space="preserve">2019-11-17</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5026,11 +5026,11 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H84">
-        <v>525</v>
+        <v>1785</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -5071,35 +5071,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brogade 67</t>
+          <t xml:space="preserve">Havnegade 14</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">7660</t>
+          <t xml:space="preserve">7620</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5010053</t>
+          <t xml:space="preserve">5720854</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H85">
-        <v>563</v>
+        <v>600</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024094</t>
+          <t xml:space="preserve">200024150</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-17</t>
+          <t xml:space="preserve">2019-11-18</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5131,35 +5131,35 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brogade 67</t>
+          <t xml:space="preserve">Fabjergstad 31A</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">7660</t>
+          <t xml:space="preserve">7620</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5010053</t>
+          <t xml:space="preserve">5009707</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H86">
-        <v>1785</v>
+        <v>428</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024094</t>
+          <t xml:space="preserve">200024461</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-17</t>
+          <t xml:space="preserve">2019-11-25</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 14</t>
+          <t xml:space="preserve">Christinelystvej 3</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5720854</t>
+          <t xml:space="preserve">5723042</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5210,16 +5210,16 @@
         </is>
       </c>
       <c r="H87">
-        <v>600</v>
+        <v>9166</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024150</t>
+          <t xml:space="preserve">200025503</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-18</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabjergstad 31A</t>
+          <t xml:space="preserve">Rådhusvænget 6</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5009707</t>
+          <t xml:space="preserve">5721214</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5270,16 +5270,16 @@
         </is>
       </c>
       <c r="H88">
-        <v>428</v>
+        <v>290</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024461</t>
+          <t xml:space="preserve">200025548</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-25</t>
+          <t xml:space="preserve">2019-12-16</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christinelystvej 3</t>
+          <t xml:space="preserve">Vasen 10</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5723042</t>
+          <t xml:space="preserve">5721112</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5330,16 +5330,16 @@
         </is>
       </c>
       <c r="H89">
-        <v>9166</v>
+        <v>402</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025503</t>
+          <t xml:space="preserve">200025547</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2019-12-16</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vasen 10</t>
+          <t xml:space="preserve">Klinkbyvænget 1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5381,25 +5381,25 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721112</t>
+          <t xml:space="preserve">5005634</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H90">
-        <v>402</v>
+        <v>885</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025547</t>
+          <t xml:space="preserve">200026062</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-16</t>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusvænget 6</t>
+          <t xml:space="preserve">Klinkbyvænget 2</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5441,25 +5441,25 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721214</t>
+          <t xml:space="preserve">5005634</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H91">
-        <v>290</v>
+        <v>560</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025548</t>
+          <t xml:space="preserve">200026065</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-16</t>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klinkbyvænget 1</t>
+          <t xml:space="preserve">Klinkbyvænget 3</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5506,15 +5506,15 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H92">
-        <v>885</v>
+        <v>560</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026062</t>
+          <t xml:space="preserve">200026065</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klinkbyvænget 2</t>
+          <t xml:space="preserve">Klinkbyvænget 5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5561,20 +5561,20 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5005634</t>
+          <t xml:space="preserve">7162232</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H93">
-        <v>560</v>
+        <v>464</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026065</t>
+          <t xml:space="preserve">200026073</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klinkbyvænget 3</t>
+          <t xml:space="preserve">Østergade 67</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5621,25 +5621,25 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5005634</t>
+          <t xml:space="preserve">5723511</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H94">
-        <v>560</v>
+        <v>413</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026065</t>
+          <t xml:space="preserve">200026149</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2019-12-23</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klinkbyvænget 5</t>
+          <t xml:space="preserve">Nissumvej 34</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">7162232</t>
+          <t xml:space="preserve">5724388</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="H95">
-        <v>464</v>
+        <v>296</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026073</t>
+          <t xml:space="preserve">200026233</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2019-12-29</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5731,35 +5731,35 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 67</t>
+          <t xml:space="preserve">Fårevej 143</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">7620</t>
+          <t xml:space="preserve">7650</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5723511</t>
+          <t xml:space="preserve">7919028</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H96">
-        <v>413</v>
+        <v>801</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026149</t>
+          <t xml:space="preserve">100148052</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-23</t>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,35 +5791,35 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nissumvej 34</t>
+          <t xml:space="preserve">Fårevej 145</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">7620</t>
+          <t xml:space="preserve">7650</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724388</t>
+          <t xml:space="preserve">7919028</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H97">
-        <v>296</v>
+        <v>688</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026233</t>
+          <t xml:space="preserve">100148052</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-29</t>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,35 +5851,35 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fårevej 145</t>
+          <t xml:space="preserve">Bredgade 17</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">7650</t>
+          <t xml:space="preserve">7620</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">7919028</t>
+          <t xml:space="preserve">5721185</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H98">
-        <v>688</v>
+        <v>768</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">100148052</t>
+          <t xml:space="preserve">200028193</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-01</t>
+          <t xml:space="preserve">2020-02-17</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5911,35 +5911,35 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fårevej 143</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">7650</t>
+          <t xml:space="preserve">7673</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">7919028</t>
+          <t xml:space="preserve">5004909</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H99">
-        <v>801</v>
+        <v>817</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">100148052</t>
+          <t xml:space="preserve">200028261</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-01</t>
+          <t xml:space="preserve">2020-02-19</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5971,35 +5971,35 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 17</t>
+          <t xml:space="preserve">Skolegade 8</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">7620</t>
+          <t xml:space="preserve">7673</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721185</t>
+          <t xml:space="preserve">5004909</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H100">
-        <v>768</v>
+        <v>4362</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028193</t>
+          <t xml:space="preserve">200028261</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-17</t>
+          <t xml:space="preserve">2020-02-19</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Skolegade 8</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6046,11 +6046,11 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H101">
-        <v>817</v>
+        <v>399</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 8</t>
+          <t xml:space="preserve">Søndergade 1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6101,25 +6101,25 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5004909</t>
+          <t xml:space="preserve">9441940</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H102">
-        <v>4362</v>
+        <v>2246</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028261</t>
+          <t xml:space="preserve">200028343</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-19</t>
+          <t xml:space="preserve">2020-02-22</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,35 +6151,35 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 8</t>
+          <t xml:space="preserve">Skolevej 7</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">7673</t>
+          <t xml:space="preserve">7680</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5004909</t>
+          <t xml:space="preserve">5007601</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H103">
-        <v>399</v>
+        <v>5595</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028261</t>
+          <t xml:space="preserve">200036608</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-19</t>
+          <t xml:space="preserve">2020-09-07</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6211,35 +6211,35 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 1</t>
+          <t xml:space="preserve">Skolevej 7</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">7673</t>
+          <t xml:space="preserve">7680</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9441940</t>
+          <t xml:space="preserve">5007601</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H104">
-        <v>2246</v>
+        <v>350</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028343</t>
+          <t xml:space="preserve">200036608</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-22</t>
+          <t xml:space="preserve">2020-09-07</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6271,35 +6271,35 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 7</t>
+          <t xml:space="preserve">Industrivej 14</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">7680</t>
+          <t xml:space="preserve">7673</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5007601</t>
+          <t xml:space="preserve">5003564</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H105">
-        <v>5595</v>
+        <v>512</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036608</t>
+          <t xml:space="preserve">200045772</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-07</t>
+          <t xml:space="preserve">2021-02-18</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6331,35 +6331,35 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 7</t>
+          <t xml:space="preserve">Solvangen 20</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">7680</t>
+          <t xml:space="preserve">7660</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5007601</t>
+          <t xml:space="preserve">100061486</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H106">
-        <v>350</v>
+        <v>745</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036608</t>
+          <t xml:space="preserve">311020719</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-07</t>
+          <t xml:space="preserve">2023-10-06</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6391,17 +6391,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 14</t>
+          <t xml:space="preserve">Nejrupvej 2C</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">7673</t>
+          <t xml:space="preserve">7620</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5003564</t>
+          <t xml:space="preserve">741039, 5005508</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6410,16 +6410,16 @@
         </is>
       </c>
       <c r="H107">
-        <v>512</v>
+        <v>2251</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045772</t>
+          <t xml:space="preserve">311028312</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-18</t>
+          <t xml:space="preserve">2023-11-25</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6451,35 +6451,35 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solvangen 20</t>
+          <t xml:space="preserve">Rammegårdvej 8</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">7660</t>
+          <t xml:space="preserve">7620</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">100061486</t>
+          <t xml:space="preserve">741033, 5006125</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H108">
-        <v>745</v>
+        <v>2198</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311020719</t>
+          <t xml:space="preserve">311028311</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-10-06</t>
+          <t xml:space="preserve">2023-11-25</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rammegårdvej 8</t>
+          <t xml:space="preserve">Ågade 14</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6521,25 +6521,25 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">741033, 5006125</t>
+          <t xml:space="preserve">338462, 338463</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H109">
-        <v>2198</v>
+        <v>2225</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311028311</t>
+          <t xml:space="preserve">311049395</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-11-25</t>
+          <t xml:space="preserve">2024-04-16</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nejrupvej 2C</t>
+          <t xml:space="preserve">Vasen 14</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">741039, 5005508</t>
+          <t xml:space="preserve">5721110</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H110">
-        <v>2251</v>
+        <v>734</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311028312</t>
+          <t xml:space="preserve">311069753</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-11-25</t>
+          <t xml:space="preserve">2024-08-22</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6646,11 +6646,11 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H111">
-        <v>734</v>
+        <v>1471</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -6706,11 +6706,11 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H112">
-        <v>1471</v>
+        <v>568</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -6766,11 +6766,11 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H113">
-        <v>568</v>
+        <v>927</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -6826,11 +6826,11 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H114">
-        <v>927</v>
+        <v>581</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vasen 14</t>
+          <t xml:space="preserve">Havnen 18</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6881,25 +6881,25 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">5721110</t>
+          <t xml:space="preserve">740998, 5721389</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H115">
-        <v>581</v>
+        <v>786</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311069753</t>
+          <t xml:space="preserve">311192944</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-08-22</t>
+          <t xml:space="preserve">2026-08-04</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 18</t>
+          <t xml:space="preserve">Havnen 92</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6941,35 +6941,35 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">740998, 5721389</t>
+          <t xml:space="preserve">741044, 7523861</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H116">
-        <v>786</v>
+        <v>363</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192944</t>
+          <t xml:space="preserve">311312790</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-04</t>
+          <t xml:space="preserve">2028-05-08</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 92</t>
+          <t xml:space="preserve">Havnen 62</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7001,25 +7001,25 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">741044, 7523861</t>
+          <t xml:space="preserve">500693, 7523861</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H117">
-        <v>363</v>
+        <v>3059</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311312790</t>
+          <t xml:space="preserve">311637293</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-08</t>
+          <t xml:space="preserve">2032-10-21</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 62</t>
+          <t xml:space="preserve">Østergade 32</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7061,25 +7061,25 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">500693, 7523861</t>
+          <t xml:space="preserve">100366309</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H118">
-        <v>3059</v>
+        <v>1232</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311637293</t>
+          <t xml:space="preserve">311641855</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-21</t>
+          <t xml:space="preserve">2032-11-10</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 32</t>
+          <t xml:space="preserve">Søndergade 2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7121,25 +7121,25 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">100366309</t>
+          <t xml:space="preserve">338409, 338410, 338411</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H119">
-        <v>1232</v>
+        <v>1180</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311641855</t>
+          <t xml:space="preserve">311664174</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-10</t>
+          <t xml:space="preserve">2033-03-04</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">

--- a/public/exports/29189935.xlsx
+++ b/public/exports/29189935.xlsx
@@ -3534,7 +3534,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017418</t>
+          <t xml:space="preserve">200017365</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025503</t>
+          <t xml:space="preserve">200025497</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">

--- a/public/exports/29189935.xlsx
+++ b/public/exports/29189935.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L119"/>
+  <dimension ref="A1:M119"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2404,10 +2599,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2464,10 +2664,15 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2524,10 +2729,15 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2584,10 +2794,15 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2644,10 +2859,15 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2704,10 +2924,15 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2764,10 +2989,15 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2824,10 +3054,15 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2884,10 +3119,15 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2944,10 +3184,15 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3004,10 +3249,15 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3064,10 +3314,15 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3124,10 +3379,15 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3184,10 +3444,15 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3244,10 +3509,15 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3304,10 +3574,15 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3364,10 +3639,15 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-03-13</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-05-14</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-10</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-10</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-24</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-24</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-31</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-22</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-28</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-28</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-29</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-10-16</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-10-27</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-10-30</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-17</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-17</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-17</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-18</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-25</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5214,20 +5644,25 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025497</t>
+          <t xml:space="preserve">200025503</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-16</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-16</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-23</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-29</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lemvig Arkitektkontor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lemvig Arkitektkontor</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-17</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-19</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-19</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-19</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-22</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-09-07</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-09-07</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lars Højris Bygge &amp; Energirådgivning</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-18</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">factum2 aalborg</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-10-06</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-11-25</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-11-25</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-04-16</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-08-22</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-08-22</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-08-22</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-08-22</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-08-22</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">THANING Miljø- og Energirådgivning</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-08-04</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-05-08</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-21</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-10</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,21 +7729,26 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-04</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L119"/>
+  <autoFilter ref="A1:M119"/>
 </worksheet>
 </file>
--- a/public/exports/29189935.xlsx
+++ b/public/exports/29189935.xlsx
@@ -5644,7 +5644,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025503</t>
+          <t xml:space="preserve">200025497</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
